--- a/2_Course/3_Term/Math_Statistics/lab_03/ЛР3_Заварзин_ИИ-б-25-6-о.xlsx
+++ b/2_Course/3_Term/Math_Statistics/lab_03/ЛР3_Заварзин_ИИ-б-25-6-о.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\SevSU\2_Course\3_Term\Math_Statistics\lab_03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\SevSU\2_Course\3_Term\Math_Statistics\lab_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF484F3-9A3F-4065-AF77-FD1997E5FFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C7F776-997A-4A60-961E-44A04525A045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Выборка X1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>№</t>
   </si>
@@ -73,13 +73,13 @@
     <t>Вывод</t>
   </si>
   <si>
-    <t>Fимп</t>
+    <t>ВАРИАЦИОННЫЙ РЯД</t>
   </si>
   <si>
-    <t>Критерии Свободы</t>
+    <t>Степени Свободы</t>
   </si>
   <si>
-    <t>p-value (двусторонний)</t>
+    <t>из таблицы</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -197,32 +197,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -257,15 +231,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1100,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
@@ -1543,10 +1515,19 @@
         <v>58.91</v>
       </c>
     </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="11"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E37">
     <sortCondition ref="E1:E37"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="D32:E32"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:B32" numberStoredAsText="1"/>
@@ -1556,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
@@ -2069,10 +2050,19 @@
         <v>55.84</v>
       </c>
     </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="11"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E41">
     <sortCondition ref="E1:E41"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="D37:E37"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:B37" numberStoredAsText="1"/>
@@ -2089,10 +2079,10 @@
     <col min="5" max="5" width="9.375" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
     <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.375" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
     <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="33.75" customWidth="1"/>
+    <col min="11" max="11" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2117,10 +2107,7 @@
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2148,16 +2135,11 @@
         <v>29</v>
       </c>
       <c r="G2" s="4">
-        <f>_xlfn.F.INV.RT(0.025,F2,F3)</f>
-        <v>2.0206783571926574</v>
-      </c>
-      <c r="H2" s="12">
-        <f>2*_xlfn.F.DIST.RT(E2,F2,F3)</f>
-        <v>1.11126095961268E-2</v>
-      </c>
-      <c r="I2" s="4" t="str">
-        <f>IF(H2&lt;0.05,"Отвергаем H0: дисперсии различаются","Нет оснований отвергнуть H0")</f>
-        <v>Отвергаем H0: дисперсии различаются</v>
+        <v>1.82</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>IF(E2&gt;G2,"Отвергаем H0","Нет оснований отвергать H0")</f>
+        <v>Отвергаем H0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2181,12 +2163,11 @@
         <v>34</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E4" t="s">
-        <v>12</v>
+      <c r="G4" s="13" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2198,8 +2179,8 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
@@ -2211,18 +2192,17 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A6:I7"/>
+    <mergeCell ref="A6:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
